--- a/Genetic algorithm/consolidation_potential_DSM_scenario1_SA4_FTE2_2026-08-04-12h27_optimized.xlsx
+++ b/Genetic algorithm/consolidation_potential_DSM_scenario1_SA4_FTE2_2026-08-04-12h27_optimized.xlsx
@@ -30,7 +30,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -39,11 +39,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00E06666"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="0093C47D"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -63,6 +68,21 @@
       <left style="medium">
         <color rgb="0066C2A5"/>
       </left>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="0066C2A5"/>
+      </left>
+      <bottom style="medium">
+        <color rgb="0066C2A5"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="medium">
+        <color rgb="0066C2A5"/>
+      </top>
+    </border>
+    <border>
       <bottom style="medium">
         <color rgb="0066C2A5"/>
       </bottom>
@@ -74,6 +94,11 @@
       <top style="medium">
         <color rgb="0066C2A5"/>
       </top>
+    </border>
+    <border>
+      <right style="medium">
+        <color rgb="0066C2A5"/>
+      </right>
     </border>
     <border>
       <right style="medium">
@@ -95,21 +120,6 @@
       <left style="medium">
         <color rgb="00E78AC3"/>
       </left>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="00E78AC3"/>
-      </left>
-      <bottom style="medium">
-        <color rgb="00E78AC3"/>
-      </bottom>
-    </border>
-    <border>
-      <top style="medium">
-        <color rgb="00E78AC3"/>
-      </top>
-    </border>
-    <border>
       <bottom style="medium">
         <color rgb="00E78AC3"/>
       </bottom>
@@ -121,11 +131,6 @@
       <top style="medium">
         <color rgb="00E78AC3"/>
       </top>
-    </border>
-    <border>
-      <right style="medium">
-        <color rgb="00E78AC3"/>
-      </right>
     </border>
     <border>
       <right style="medium">
@@ -147,6 +152,21 @@
       <left style="medium">
         <color rgb="00E5C494"/>
       </left>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00E5C494"/>
+      </left>
+      <bottom style="medium">
+        <color rgb="00E5C494"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="medium">
+        <color rgb="00E5C494"/>
+      </top>
+    </border>
+    <border>
       <bottom style="medium">
         <color rgb="00E5C494"/>
       </bottom>
@@ -163,6 +183,11 @@
       <right style="medium">
         <color rgb="00E5C494"/>
       </right>
+    </border>
+    <border>
+      <right style="medium">
+        <color rgb="00E5C494"/>
+      </right>
       <bottom style="medium">
         <color rgb="00E5C494"/>
       </bottom>
@@ -171,29 +196,34 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -565,159 +595,159 @@
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
+          <t>Clinical Strategy Group</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>Strategic Management Team 1</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Strategic Management Team 3</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Operational Effectiveness</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Strategic Management Team 2</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
         <is>
           <t>Clinical Research Division</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Clinical Strategy Division</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Clinical Strategy Group</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Medical Communications Office</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Medical Evaluation Unit 1</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Medical Evaluation Unit 2</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Medical Evaluation Unit 3</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Medical Excellence Office</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Medical Excellence Team</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Medical Governance Office</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Medical Governance Unit</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Medical Innovation Group</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Medical Research Evaluation</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Medical Scientific Information Center</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>New Product Value Planning</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Operational Excellence</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Post-Marketing Study Strategy Management</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Product Management Review</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Regulatory Affairs Unit 1</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Regulatory Affairs Unit 2</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Regulatory Affairs Unit 3</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Scientific Information Center</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Strategic Management Office 1</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Strategic Management Office 2</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Strategic Management Office 3</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Strategic Medical Excellence</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>Operational Effectiveness</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>Strategic Management Team 2</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Strategic Management Team 1</t>
+          <t>Clinical Strategy Group</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
@@ -726,7 +756,7 @@
       <c r="C2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
@@ -735,11 +765,11 @@
       <c r="F2" t="n">
         <v>0</v>
       </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
+      <c r="G2" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>5.5</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -768,11 +798,11 @@
       <c r="Q2" t="n">
         <v>0</v>
       </c>
-      <c r="R2" t="n">
+      <c r="R2" s="4" t="n">
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -784,7 +814,7 @@
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -793,13 +823,13 @@
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.18</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -814,16 +844,16 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Strategic Management Team 3</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
+          <t>Strategic Management Team 1</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
@@ -869,13 +899,13 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -890,19 +920,19 @@
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.880000000000001</v>
+        <v>5.18</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE3" t="n">
         <v>0</v>
@@ -911,95 +941,95 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Clinical Research Division</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>4.79</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I4" s="7" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="J4" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="7" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="N4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="P4" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" s="7" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="V4" s="7" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="W4" s="7" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="X4" s="7" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="Y4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="8" t="n">
-        <v>0</v>
+          <t>Strategic Management Team 3</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>3</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
@@ -1008,7 +1038,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Clinical Strategy Division</t>
+          <t>Operational Effectiveness</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -1017,26 +1047,26 @@
       <c r="C5" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="9" t="n">
-        <v>4.74</v>
-      </c>
-      <c r="E5" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="F5" s="10" t="n">
-        <v>5.5</v>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -1045,16 +1075,16 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>4</v>
-      </c>
-      <c r="P5" s="10" t="n">
-        <v>7</v>
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1069,34 +1099,34 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
+        <v>12.88</v>
+      </c>
+      <c r="V5" t="n">
         <v>2</v>
       </c>
-      <c r="V5" t="n">
-        <v>4.75</v>
-      </c>
       <c r="W5" t="n">
-        <v>4.71</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC5" t="n">
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
@@ -1105,7 +1135,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Clinical Strategy Group</t>
+          <t>Strategic Management Team 2</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1114,13 +1144,13 @@
       <c r="C6" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E6" s="10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F6" t="n">
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="13" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
@@ -1148,9 +1178,9 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
@@ -1166,7 +1196,7 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1187,10 +1217,10 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>14.67</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1202,16 +1232,16 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Medical Communications Office</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0</v>
+          <t>Clinical Research Division</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>2</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="12" t="n">
+      <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
@@ -1220,183 +1250,183 @@
       <c r="F7" t="n">
         <v>0</v>
       </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="L7" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="10" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="P7" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q7" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>15</v>
-      </c>
-      <c r="U7" s="10" t="n">
+      <c r="G7" s="14" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="H7" s="15" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="I7" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="16" t="n">
         <v>1.5</v>
       </c>
-      <c r="V7" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="W7" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="X7" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y7" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
+      <c r="K7" s="16" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="L7" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P7" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="S7" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" s="16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X7" s="16" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="Y7" s="16" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="Z7" s="16" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AA7" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Medical Evaluation Unit 1</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0</v>
+          <t>Clinical Strategy Division</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>5.5</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="12" t="n">
-        <v>1.5</v>
+      <c r="D8" t="n">
+        <v>0</v>
       </c>
       <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="18" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
         <v>1.4</v>
       </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
+      <c r="K8" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R8" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
         <v>2</v>
       </c>
-      <c r="H8" t="n">
-        <v>6.24</v>
-      </c>
-      <c r="I8" s="10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="K8" s="10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L8" s="10" t="n">
-        <v>6.22</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="O8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1</v>
-      </c>
-      <c r="V8" s="10" t="n">
-        <v>8.949999999999999</v>
-      </c>
-      <c r="W8" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="X8" s="10" t="n">
-        <v>10</v>
+      <c r="X8" t="n">
+        <v>4.75</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.82</v>
+        <v>4.71</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.33</v>
+        <v>3.21</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC8" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.4</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="AE8" s="20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Medical Evaluation Unit 2</t>
+          <t>Medical Communications Office</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1405,95 +1435,95 @@
       <c r="C9" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="12" t="n">
-        <v>3.4</v>
+      <c r="D9" t="n">
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="10" t="n">
-        <v>4.7</v>
+      <c r="G9" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>6.41</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K9" s="10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L9" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="M9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="N9" t="n">
+      <c r="N9" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="19" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" s="10" t="n">
+      <c r="R9" t="n">
+        <v>12</v>
+      </c>
+      <c r="S9" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="T9" t="n">
         <v>2</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>15</v>
+      </c>
+      <c r="W9" s="19" t="n">
         <v>1.5</v>
       </c>
-      <c r="U9" t="n">
-        <v>1</v>
-      </c>
-      <c r="V9" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="W9" s="10" t="n">
-        <v>7.66</v>
-      </c>
-      <c r="X9" s="10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Y9" t="n">
+      <c r="X9" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="Y9" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z9" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AA9" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
         <v>2</v>
       </c>
-      <c r="AA9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="11" t="n">
+      <c r="AC9" t="n">
         <v>0</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
       </c>
-      <c r="AE9" t="n">
-        <v>0</v>
+      <c r="AE9" s="20" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Medical Evaluation Unit 3</t>
+          <t>Medical Evaluation Unit 1</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1502,8 +1532,8 @@
       <c r="C10" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="12" t="n">
-        <v>1</v>
+      <c r="D10" t="n">
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -1511,86 +1541,86 @@
       <c r="F10" t="n">
         <v>0</v>
       </c>
-      <c r="G10" t="n">
-        <v>1</v>
+      <c r="G10" s="21" t="n">
+        <v>1.5</v>
       </c>
       <c r="H10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="K10" s="19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L10" t="n">
         <v>3.53</v>
       </c>
-      <c r="I10" t="n">
-        <v>5</v>
-      </c>
-      <c r="J10" t="n">
-        <v>5.44</v>
-      </c>
-      <c r="K10" s="10" t="n">
+      <c r="M10" s="19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N10" s="19" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R10" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>2</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" s="19" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="Y10" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z10" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="L10" s="10" t="n">
+      <c r="AA10" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
         <v>2</v>
       </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="O10" t="n">
+      <c r="AE10" s="20" t="n">
         <v>2</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="W10" t="n">
-        <v>3</v>
-      </c>
-      <c r="X10" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Medical Excellence Office</t>
+          <t>Medical Evaluation Unit 2</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1599,7 +1629,7 @@
       <c r="C11" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="12" t="n">
+      <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
@@ -1608,86 +1638,86 @@
       <c r="F11" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="10" t="n">
+      <c r="G11" s="21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K11" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="L11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M11" s="19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N11" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="H11" s="10" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="I11" s="10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J11" s="10" t="n">
+      <c r="O11" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="10" t="n">
+      <c r="Y11" s="19" t="n">
+        <v>7.66</v>
+      </c>
+      <c r="Z11" s="19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC11" t="n">
         <v>1.5</v>
       </c>
-      <c r="P11" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2</v>
-      </c>
-      <c r="R11" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>10</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1</v>
-      </c>
-      <c r="V11" s="10" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="W11" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="X11" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y11" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" s="13" t="n">
-        <v>10</v>
-      </c>
       <c r="AD11" t="n">
         <v>0</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AE11" s="20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Medical Excellence Team</t>
+          <t>Medical Evaluation Unit 3</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1696,7 +1726,7 @@
       <c r="C12" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="12" t="n">
+      <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
@@ -1705,86 +1735,86 @@
       <c r="F12" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="10" t="n">
-        <v>8.67</v>
-      </c>
-      <c r="I12" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="J12" s="10" t="n">
+      <c r="G12" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="K12" t="n">
+        <v>5</v>
+      </c>
+      <c r="L12" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="M12" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="N12" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="K12" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="10" t="n">
-        <v>0</v>
+      <c r="O12" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" t="n">
+        <v>4.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R12" t="n">
         <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="10" t="n">
-        <v>5.13</v>
-      </c>
-      <c r="W12" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="V12" t="n">
+        <v>2</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>3</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
       </c>
-      <c r="AE12" t="n">
-        <v>0</v>
+      <c r="AE12" s="20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Medical Governance Office</t>
+          <t>Medical Excellence Office</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1793,95 +1823,95 @@
       <c r="C13" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="12" t="n">
-        <v>1.28</v>
+      <c r="D13" t="n">
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="10" t="n">
-        <v>3</v>
+      <c r="G13" s="21" t="n">
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="10" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="I13" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="J13" s="19" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="K13" s="19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L13" s="19" t="n">
+        <v>10</v>
       </c>
       <c r="M13" t="n">
-        <v>7.33</v>
-      </c>
-      <c r="N13" t="n">
-        <v>6</v>
-      </c>
-      <c r="O13" t="n">
-        <v>3.43</v>
+        <v>0</v>
+      </c>
+      <c r="N13" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="19" t="n">
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Q13" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="19" t="n">
         <v>1.5</v>
       </c>
+      <c r="R13" s="19" t="n">
+        <v>0</v>
+      </c>
       <c r="S13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.13</v>
+        <v>2</v>
+      </c>
+      <c r="T13" s="19" t="n">
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>2</v>
-      </c>
-      <c r="W13" s="10" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="X13" s="10" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Y13" s="10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.8</v>
+        <v>10</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" s="19" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="Y13" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z13" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA13" s="19" t="n">
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC13" s="11" t="n">
-        <v>13.5</v>
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
       </c>
-      <c r="AE13" t="n">
-        <v>1</v>
+      <c r="AE13" s="22" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Medical Governance Unit</t>
+          <t>Medical Excellence Team</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1890,7 +1920,7 @@
       <c r="C14" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="12" t="n">
+      <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
@@ -1899,86 +1929,86 @@
       <c r="F14" t="n">
         <v>0</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="J14" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="I14" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="19" t="n">
+        <v>8.67</v>
+      </c>
+      <c r="K14" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="L14" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="M14" s="19" t="n">
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
-      <c r="O14" t="n">
-        <v>2</v>
+      <c r="O14" s="19" t="n">
+        <v>0</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
+      <c r="Q14" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="19" t="n">
         <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T14" s="19" t="n">
         <v>0</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1</v>
-      </c>
-      <c r="X14" t="n">
-        <v>5.33</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" s="19" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="Y14" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="19" t="n">
         <v>0</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
       </c>
-      <c r="AC14" s="11" t="n">
+      <c r="AC14" t="n">
         <v>0</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
       </c>
-      <c r="AE14" t="n">
+      <c r="AE14" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Medical Innovation Group</t>
+          <t>Medical Governance Office</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1987,95 +2017,95 @@
       <c r="C15" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="12" t="n">
-        <v>1</v>
+      <c r="D15" t="n">
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="10" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="G15" s="21" t="n">
+        <v>1.28</v>
       </c>
       <c r="H15" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="I15" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J15" t="n">
         <v>1.25</v>
       </c>
-      <c r="I15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="P15" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S15" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V15" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X15" t="n">
         <v>2</v>
       </c>
-      <c r="K15" s="10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L15" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="N15" t="n">
-        <v>2</v>
-      </c>
-      <c r="O15" t="n">
-        <v>7.63</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q15" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>2</v>
-      </c>
-      <c r="S15" t="n">
+      <c r="Y15" s="19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z15" s="19" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AA15" s="19" t="n">
         <v>1.33</v>
       </c>
-      <c r="T15" t="n">
-        <v>2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1</v>
-      </c>
-      <c r="V15" t="n">
-        <v>5.33</v>
-      </c>
-      <c r="W15" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="Y15" s="10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>4</v>
-      </c>
       <c r="AB15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC15" s="11" t="n">
-        <v>12.5</v>
+        <v>1.25</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.6</v>
+      </c>
+      <c r="AE15" s="20" t="n">
+        <v>13.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Medical Research Evaluation</t>
+          <t>Medical Governance Unit</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -2084,95 +2114,95 @@
       <c r="C16" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="9" t="n">
-        <v>5.63</v>
-      </c>
-      <c r="E16" s="10" t="n">
-        <v>10.67</v>
-      </c>
-      <c r="F16" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>12</v>
-      </c>
-      <c r="H16" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="10" t="n">
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="L16" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>6</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
         <v>2</v>
       </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.5</v>
-      </c>
       <c r="R16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>7</v>
-      </c>
-      <c r="V16" s="10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="W16" s="10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="X16" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
         <v>2</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z16" t="n">
-        <v>2</v>
+        <v>5.33</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC16" s="11" t="n">
-        <v>7</v>
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
       </c>
-      <c r="AE16" t="n">
+      <c r="AE16" s="20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Medical Scientific Information Center</t>
+          <t>Medical Innovation Group</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2181,7 +2211,7 @@
       <c r="C17" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="12" t="n">
+      <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
@@ -2190,396 +2220,396 @@
       <c r="F17" t="n">
         <v>0</v>
       </c>
-      <c r="G17" s="10" t="n">
-        <v>6</v>
+      <c r="G17" s="21" t="n">
+        <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
+        <v>2.5</v>
+      </c>
+      <c r="I17" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
         <v>2</v>
       </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" s="10" t="n">
-        <v>0</v>
+      <c r="M17" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N17" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3.43</v>
       </c>
       <c r="P17" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>7.63</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" s="19" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="U17" s="10" t="n">
-        <v>18.75</v>
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.33</v>
       </c>
       <c r="V17" t="n">
+        <v>2</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1</v>
+      </c>
+      <c r="X17" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AA17" s="19" t="n">
         <v>1.5</v>
       </c>
-      <c r="W17" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="X17" s="10" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y17" s="10" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
       <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" s="11" t="n">
-        <v>6</v>
+        <v>1.67</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>4</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="AE17" s="20" t="n">
+        <v>12.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>New Product Value Planning</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
+          <t>Medical Research Evaluation</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
-      <c r="D18" s="12" t="n">
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="18" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="H18" s="19" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="I18" t="n">
+        <v>12</v>
+      </c>
+      <c r="J18" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>7</v>
+      </c>
+      <c r="W18" t="n">
+        <v>7</v>
+      </c>
+      <c r="X18" s="19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y18" s="19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Z18" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="H18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K18" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
         <v>2</v>
       </c>
-      <c r="P18" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V18" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="W18" t="n">
-        <v>2</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC18" s="11" t="n">
-        <v>8.5</v>
+      <c r="AC18" t="n">
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AE18" s="20" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Operational Excellence</t>
+          <t>Medical Scientific Information Center</t>
         </is>
       </c>
       <c r="B19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
         <v>2</v>
       </c>
-      <c r="C19" t="n">
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W19" s="19" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Y19" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="D19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>14.69</v>
-      </c>
-      <c r="T19" t="n">
-        <v>7.67</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>3.53</v>
+      <c r="Z19" s="19" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA19" s="19" t="n">
+        <v>7.75</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="AC19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
         <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>6.5</v>
+        <v>0</v>
+      </c>
+      <c r="AE19" s="20" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Post-Marketing Study Strategy Management</t>
+          <t>New Product Value Planning</t>
         </is>
       </c>
       <c r="B20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M20" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
         <v>1.5</v>
       </c>
-      <c r="C20" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="D20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>15</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>10</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.4</v>
-      </c>
       <c r="P20" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.5</v>
+        <v>2</v>
       </c>
       <c r="R20" t="n">
         <v>1</v>
       </c>
       <c r="S20" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>9.33</v>
+        <v>3.38</v>
       </c>
       <c r="U20" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>5.5</v>
+        <v>2</v>
       </c>
       <c r="W20" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="X20" t="n">
-        <v>3</v>
+        <v>4.67</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="10" t="n">
-        <v>5.9</v>
+        <v>2</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.64</v>
       </c>
       <c r="AA20" t="n">
-        <v>6.07</v>
+        <v>2</v>
       </c>
       <c r="AB20" t="n">
-        <v>5.94</v>
-      </c>
-      <c r="AC20" s="11" t="n">
-        <v>5.5</v>
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="AE20" s="20" t="n">
+        <v>8.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Product Management Review</t>
+          <t>Operational Excellence</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3</v>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>13.5</v>
       </c>
       <c r="F21" t="n">
-        <v>10</v>
-      </c>
-      <c r="G21" s="10" t="n">
-        <v>1.67</v>
+        <v>6.5</v>
+      </c>
+      <c r="G21" s="21" t="n">
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -2591,267 +2621,267 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="P21" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q21" s="10" t="n">
-        <v>18.75</v>
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.5</v>
       </c>
       <c r="R21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>16.17</v>
+        <v>14.69</v>
       </c>
       <c r="V21" t="n">
-        <v>1.67</v>
+        <v>7.67</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Y21" s="10" t="n">
-        <v>4.23</v>
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
         <v>1</v>
       </c>
       <c r="AA21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC21" s="11" t="n">
-        <v>4</v>
+        <v>3.55</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>3.53</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="AE21" s="20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Regulatory Affairs Unit 1</t>
+          <t>Post-Marketing Study Strategy Management</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="12" t="n">
-        <v>5.21</v>
+        <v>1.5</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.67</v>
       </c>
       <c r="E22" t="n">
-        <v>4.77</v>
+        <v>1.5</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
+        <v>4</v>
+      </c>
+      <c r="G22" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>15</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>10</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
         <v>6.25</v>
       </c>
-      <c r="H22" s="10" t="n">
-        <v>8.949999999999999</v>
-      </c>
-      <c r="I22" s="10" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="J22" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="K22" s="10" t="n">
+      <c r="V22" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="X22" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z22" t="n">
         <v>3</v>
       </c>
-      <c r="L22" s="10" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="N22" t="n">
-        <v>2</v>
-      </c>
-      <c r="O22" t="n">
-        <v>5.33</v>
-      </c>
-      <c r="P22" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R22" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V22" t="n">
-        <v>7.06</v>
-      </c>
-      <c r="W22" s="10" t="n">
-        <v>6.67</v>
-      </c>
-      <c r="X22" s="10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>7.29</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>4.25</v>
-      </c>
       <c r="AA22" t="n">
         <v>0</v>
       </c>
-      <c r="AB22" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC22" s="11" t="n">
-        <v>10</v>
+      <c r="AB22" s="19" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>6.07</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>0</v>
+        <v>5.94</v>
+      </c>
+      <c r="AE22" s="20" t="n">
+        <v>5.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Regulatory Affairs Unit 2</t>
+          <t>Product Management Review</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
       </c>
-      <c r="D23" s="12" t="n">
-        <v>3.07</v>
+      <c r="D23" t="n">
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
-      <c r="G23" s="10" t="n">
+      <c r="G23" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" s="19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
         <v>7</v>
       </c>
-      <c r="H23" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="I23" s="10" t="n">
-        <v>7.66</v>
-      </c>
-      <c r="J23" t="n">
-        <v>3</v>
-      </c>
-      <c r="K23" s="10" t="n">
+      <c r="S23" s="19" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="T23" t="n">
         <v>4</v>
       </c>
-      <c r="L23" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" s="10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="N23" t="n">
-        <v>1</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="P23" s="10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Q23" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3</v>
-      </c>
       <c r="U23" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="V23" s="10" t="n">
-        <v>6.33</v>
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.33</v>
       </c>
       <c r="W23" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="X23" s="10" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="Y23" s="10" t="n">
-        <v>3.14</v>
+        <v>16.17</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>5.1</v>
+        <v>1.33</v>
+      </c>
+      <c r="AA23" s="19" t="n">
+        <v>4.23</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC23" s="11" t="n">
-        <v>6</v>
+        <v>1</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>4</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="AE23" s="20" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Regulatory Affairs Unit 3</t>
+          <t>Regulatory Affairs Unit 1</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -2860,95 +2890,95 @@
       <c r="C24" t="n">
         <v>0</v>
       </c>
-      <c r="D24" s="12" t="n">
-        <v>1.63</v>
+      <c r="D24" t="n">
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
-      <c r="G24" s="10" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="H24" s="10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="I24" s="10" t="n">
+      <c r="G24" s="21" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="H24" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="I24" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="J24" s="19" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="K24" s="19" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="L24" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="M24" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="N24" s="19" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="R24" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="S24" t="n">
         <v>1.5</v>
       </c>
-      <c r="J24" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="K24" s="10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L24" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" s="10" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="N24" t="n">
-        <v>5.33</v>
-      </c>
-      <c r="O24" t="n">
-        <v>2</v>
-      </c>
-      <c r="P24" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q24" s="10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R24" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="S24" t="n">
-        <v>1</v>
-      </c>
       <c r="T24" t="n">
-        <v>3.33</v>
+        <v>4.5</v>
       </c>
       <c r="U24" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="V24" s="10" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="W24" s="10" t="n">
-        <v>2.67</v>
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.42</v>
       </c>
       <c r="X24" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="Y24" s="10" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.5</v>
+        <v>7.06</v>
+      </c>
+      <c r="Y24" s="19" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="Z24" s="19" t="n">
+        <v>2.4</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.5</v>
+        <v>7.29</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC24" s="11" t="n">
-        <v>4</v>
+        <v>4.25</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.67</v>
+      </c>
+      <c r="AE24" s="20" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Scientific Information Center</t>
+          <t>Regulatory Affairs Unit 2</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -2957,7 +2987,7 @@
       <c r="C25" t="n">
         <v>0</v>
       </c>
-      <c r="D25" s="12" t="n">
+      <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
@@ -2966,95 +2996,95 @@
       <c r="F25" t="n">
         <v>0</v>
       </c>
-      <c r="G25" s="10" t="n">
-        <v>0</v>
+      <c r="G25" s="21" t="n">
+        <v>3.07</v>
       </c>
       <c r="H25" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="I25" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="J25" t="n">
         <v>4.75</v>
       </c>
-      <c r="K25" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" s="10" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="N25" t="n">
-        <v>1</v>
-      </c>
-      <c r="O25" s="10" t="n">
-        <v>1.33</v>
+      <c r="I25" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="J25" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="K25" s="19" t="n">
+        <v>7.66</v>
+      </c>
+      <c r="L25" t="n">
+        <v>3</v>
+      </c>
+      <c r="M25" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="N25" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="19" t="n">
+        <v>1.5</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="10" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="R25" t="n">
-        <v>2</v>
-      </c>
-      <c r="S25" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="R25" s="19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="S25" s="19" t="n">
+        <v>3</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" s="10" t="n">
-        <v>3.83</v>
+        <v>1.6</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>7.29</v>
-      </c>
-      <c r="W25" s="10" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="X25" s="10" t="n">
-        <v>4.2</v>
+        <v>3</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X25" s="19" t="n">
+        <v>6.33</v>
       </c>
       <c r="Y25" t="n">
-        <v>7.95</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1</v>
+        <v>4.75</v>
+      </c>
+      <c r="Z25" s="19" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AA25" s="19" t="n">
+        <v>3.14</v>
       </c>
       <c r="AB25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC25" s="11" t="n">
-        <v>0</v>
+        <v>4.5</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>5.1</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
       </c>
-      <c r="AE25" t="n">
-        <v>0</v>
+      <c r="AE25" s="20" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Strategic Management Office 1</t>
+          <t>Regulatory Affairs Unit 3</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>6</v>
-      </c>
-      <c r="D26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
@@ -3063,395 +3093,395 @@
       <c r="F26" t="n">
         <v>0</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G26" s="21" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="I26" s="19" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="J26" s="19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K26" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L26" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="M26" s="19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N26" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P26" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="Q26" t="n">
         <v>2</v>
       </c>
-      <c r="H26" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="I26" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="J26" t="n">
-        <v>1</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="N26" t="n">
-        <v>1</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="P26" t="n">
+      <c r="R26" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="T26" s="10" t="n">
-        <v>5.93</v>
+      <c r="S26" s="19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.92</v>
       </c>
       <c r="U26" t="n">
         <v>1</v>
       </c>
       <c r="V26" t="n">
-        <v>4.25</v>
+        <v>3.33</v>
       </c>
       <c r="W26" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="X26" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X26" s="19" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Y26" s="19" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="AA26" s="19" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AB26" t="n">
         <v>1.5</v>
       </c>
-      <c r="Y26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>5.66</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>6.67</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>5.29</v>
-      </c>
-      <c r="AC26" s="11" t="n">
-        <v>0</v>
+      <c r="AC26" t="n">
+        <v>2.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>8</v>
+        <v>2.5</v>
+      </c>
+      <c r="AE26" s="20" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Strategic Management Office 2</t>
+          <t>Scientific Information Center</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
-      </c>
-      <c r="D27" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
-      <c r="G27" t="n">
-        <v>1.5</v>
+      <c r="G27" s="21" t="n">
+        <v>0</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
-      <c r="I27" t="n">
+      <c r="I27" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="L27" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="M27" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q27" s="19" t="n">
         <v>1.33</v>
       </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>4</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
-      <c r="S27" t="n">
-        <v>3.47</v>
+      <c r="S27" s="19" t="n">
+        <v>6.6</v>
       </c>
       <c r="T27" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="U27" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
       </c>
-      <c r="W27" t="n">
-        <v>6</v>
+      <c r="W27" s="19" t="n">
+        <v>3.83</v>
       </c>
       <c r="X27" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>6.88</v>
+        <v>7.29</v>
+      </c>
+      <c r="Y27" s="19" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="Z27" s="19" t="n">
+        <v>4.2</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.55</v>
+        <v>7.95</v>
       </c>
       <c r="AB27" t="n">
-        <v>6.77</v>
-      </c>
-      <c r="AC27" s="11" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>14.67</v>
+        <v>1</v>
+      </c>
+      <c r="AE27" s="20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Strategic Management Office 3</t>
+          <t>Strategic Management Office 1</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>11</v>
-      </c>
-      <c r="D28" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="D28" t="n">
+        <v>6</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" t="n">
+        <v>8</v>
+      </c>
+      <c r="G28" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
         <v>2</v>
       </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
       </c>
       <c r="O28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R28" t="n">
         <v>2</v>
       </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
       <c r="S28" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>6.58</v>
+        <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="V28" t="n">
-        <v>2</v>
+        <v>3.43</v>
+      </c>
+      <c r="V28" s="19" t="n">
+        <v>5.93</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X28" t="n">
-        <v>2.5</v>
+        <v>4.25</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>6.46</v>
+        <v>1.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>6.46</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>5.86</v>
-      </c>
-      <c r="AC28" s="11" t="n">
-        <v>0</v>
+        <v>5.66</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>6.67</v>
       </c>
       <c r="AD28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE28" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="AE28" s="20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Strategic Medical Excellence</t>
+          <t>Strategic Management Office 2</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="15" t="n">
-        <v>20</v>
-      </c>
-      <c r="H29" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="I29" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" s="16" t="n">
         <v>10</v>
       </c>
-      <c r="L29" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" s="15" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="N29" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" s="15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="P29" s="15" t="n">
+      <c r="D29" t="n">
+        <v>3</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>14.67</v>
+      </c>
+      <c r="G29" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>4</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="V29" t="n">
         <v>7</v>
       </c>
-      <c r="Q29" s="15" t="n">
+      <c r="W29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
         <v>6</v>
       </c>
-      <c r="R29" s="15" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="S29" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" s="15" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="U29" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="V29" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="W29" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="X29" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y29" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA29" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB29" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC29" s="17" t="n">
-        <v>0</v>
+      <c r="Z29" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>3.55</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="n">
+        <v>6.77</v>
+      </c>
+      <c r="AE29" s="20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Operational Effectiveness</t>
+          <t>Strategic Management Office 3</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
-      <c r="G30" t="n">
+      <c r="G30" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
@@ -3461,7 +3491,7 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -3476,61 +3506,61 @@
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="P30" t="n">
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>12.88</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="V30" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X30" t="n">
         <v>2</v>
       </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0</v>
-      </c>
       <c r="Y30" t="n">
         <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1</v>
+        <v>6.46</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD30" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE30" s="19" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="AE30" s="20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Strategic Management Team 2</t>
+          <t>Strategic Medical Excellence</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -3548,79 +3578,79 @@
       <c r="F31" t="n">
         <v>0</v>
       </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>1</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>8</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>14.67</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD31" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE31" s="21" t="n">
+      <c r="G31" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="24" t="n">
+        <v>20</v>
+      </c>
+      <c r="J31" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="K31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="N31" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="P31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="R31" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="S31" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="T31" s="24" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="U31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" s="24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W31" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="X31" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y31" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z31" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3641,159 +3671,159 @@
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
+          <t>Clinical Strategy Group</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>Strategic Management Team 1</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Strategic Management Team 3</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Operational Effectiveness</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Strategic Management Team 2</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
         <is>
           <t>Clinical Research Division</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Clinical Strategy Division</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Clinical Strategy Group</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Medical Communications Office</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Medical Evaluation Unit 1</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Medical Evaluation Unit 2</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Medical Evaluation Unit 3</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Medical Excellence Office</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Medical Excellence Team</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Medical Governance Office</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Medical Governance Unit</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Medical Innovation Group</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Medical Research Evaluation</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Medical Scientific Information Center</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>New Product Value Planning</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Operational Excellence</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Post-Marketing Study Strategy Management</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Product Management Review</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Regulatory Affairs Unit 1</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Regulatory Affairs Unit 2</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Regulatory Affairs Unit 3</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Scientific Information Center</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Strategic Management Office 1</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Strategic Management Office 2</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Strategic Management Office 3</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Strategic Medical Excellence</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>Operational Effectiveness</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>Strategic Management Team 2</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Strategic Management Team 1</t>
+          <t>Clinical Strategy Group</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
@@ -3802,7 +3832,7 @@
       <c r="C2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
@@ -3811,11 +3841,11 @@
       <c r="F2" t="n">
         <v>0</v>
       </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
+      <c r="G2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -3844,8 +3874,8 @@
       <c r="Q2" t="n">
         <v>0</v>
       </c>
-      <c r="R2" t="n">
-        <v>0</v>
+      <c r="R2" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -3890,16 +3920,16 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Strategic Management Team 3</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
+          <t>Strategic Management Team 1</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
@@ -3987,91 +4017,91 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Clinical Research Division</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="8" t="n">
+          <t>Strategic Management Team 3</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
         <v>0</v>
       </c>
       <c r="AD4" t="n">
@@ -4084,7 +4114,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Clinical Strategy Division</t>
+          <t>Operational Effectiveness</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -4093,14 +4123,14 @@
       <c r="C5" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="10" t="n">
-        <v>1</v>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -4129,8 +4159,8 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="P5" s="10" t="n">
-        <v>1</v>
+      <c r="P5" t="n">
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -4168,7 +4198,7 @@
       <c r="AB5" t="n">
         <v>0</v>
       </c>
-      <c r="AC5" s="11" t="n">
+      <c r="AC5" t="n">
         <v>0</v>
       </c>
       <c r="AD5" t="n">
@@ -4181,7 +4211,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Clinical Strategy Group</t>
+          <t>Strategic Management Team 2</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -4190,13 +4220,13 @@
       <c r="C6" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" t="n">
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="13" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
@@ -4226,8 +4256,8 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="P6" s="10" t="n">
-        <v>1</v>
+      <c r="P6" t="n">
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -4265,7 +4295,7 @@
       <c r="AB6" t="n">
         <v>0</v>
       </c>
-      <c r="AC6" s="11" t="n">
+      <c r="AC6" t="n">
         <v>0</v>
       </c>
       <c r="AD6" t="n">
@@ -4278,16 +4308,16 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Medical Communications Office</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0</v>
+          <t>Clinical Research Division</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="12" t="n">
+      <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
@@ -4296,95 +4326,95 @@
       <c r="F7" t="n">
         <v>0</v>
       </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="X7" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y7" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
+      <c r="G7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Medical Evaluation Unit 1</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0</v>
+          <t>Clinical Strategy Division</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="12" t="n">
+      <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
@@ -4393,23 +4423,23 @@
       <c r="F8" t="n">
         <v>0</v>
       </c>
-      <c r="G8" t="n">
-        <v>0</v>
+      <c r="G8" s="18" t="n">
+        <v>1</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
-      <c r="I8" s="10" t="n">
-        <v>1</v>
+      <c r="I8" t="n">
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
-      <c r="K8" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" s="10" t="n">
-        <v>1</v>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -4420,14 +4450,14 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="P8" s="10" t="n">
-        <v>1</v>
+      <c r="P8" t="n">
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
-      <c r="R8" t="n">
-        <v>0</v>
+      <c r="R8" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -4438,14 +4468,14 @@
       <c r="U8" t="n">
         <v>0</v>
       </c>
-      <c r="V8" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="W8" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="X8" s="10" t="n">
-        <v>1</v>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
@@ -4459,20 +4489,20 @@
       <c r="AB8" t="n">
         <v>0</v>
       </c>
-      <c r="AC8" s="11" t="n">
+      <c r="AC8" t="n">
         <v>0</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="AE8" s="20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Medical Evaluation Unit 2</t>
+          <t>Medical Communications Office</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -4481,7 +4511,7 @@
       <c r="C9" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="12" t="n">
+      <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
@@ -4490,11 +4520,11 @@
       <c r="F9" t="n">
         <v>0</v>
       </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="10" t="n">
-        <v>1</v>
+      <c r="G9" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -4502,32 +4532,32 @@
       <c r="J9" t="n">
         <v>0</v>
       </c>
-      <c r="K9" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
-      <c r="S9" t="n">
-        <v>0</v>
+      <c r="S9" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -4535,41 +4565,41 @@
       <c r="U9" t="n">
         <v>0</v>
       </c>
-      <c r="V9" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="W9" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="X9" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0</v>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z9" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA9" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
       </c>
-      <c r="AC9" s="11" t="n">
+      <c r="AC9" t="n">
         <v>0</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AE9" s="20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Medical Evaluation Unit 3</t>
+          <t>Medical Evaluation Unit 1</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -4578,7 +4608,7 @@
       <c r="C10" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="12" t="n">
+      <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
@@ -4587,7 +4617,7 @@
       <c r="F10" t="n">
         <v>0</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
@@ -4599,17 +4629,17 @@
       <c r="J10" t="n">
         <v>0</v>
       </c>
-      <c r="K10" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
+      <c r="K10" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -4620,8 +4650,8 @@
       <c r="Q10" t="n">
         <v>0</v>
       </c>
-      <c r="R10" t="n">
-        <v>0</v>
+      <c r="R10" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -4638,14 +4668,14 @@
       <c r="W10" t="n">
         <v>0</v>
       </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
+      <c r="X10" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z10" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -4653,20 +4683,20 @@
       <c r="AB10" t="n">
         <v>0</v>
       </c>
-      <c r="AC10" s="11" t="n">
+      <c r="AC10" t="n">
         <v>0</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AE10" s="20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Medical Excellence Office</t>
+          <t>Medical Evaluation Unit 2</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -4675,7 +4705,7 @@
       <c r="C11" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="12" t="n">
+      <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
@@ -4684,40 +4714,40 @@
       <c r="F11" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" s="10" t="n">
+      <c r="G11" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="19" t="n">
         <v>1</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="P11" s="10" t="n">
-        <v>1</v>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
-      <c r="R11" s="10" t="n">
+      <c r="R11" s="19" t="n">
         <v>1</v>
       </c>
       <c r="S11" t="n">
@@ -4729,20 +4759,20 @@
       <c r="U11" t="n">
         <v>0</v>
       </c>
-      <c r="V11" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="W11" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="X11" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y11" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0</v>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z11" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -4750,20 +4780,20 @@
       <c r="AB11" t="n">
         <v>0</v>
       </c>
-      <c r="AC11" s="13" t="n">
-        <v>1</v>
+      <c r="AC11" t="n">
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AE11" s="20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Medical Excellence Team</t>
+          <t>Medical Evaluation Unit 3</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -4772,7 +4802,7 @@
       <c r="C12" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="12" t="n">
+      <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
@@ -4781,41 +4811,41 @@
       <c r="F12" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" s="10" t="n">
-        <v>1</v>
+      <c r="G12" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
-      <c r="M12" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="P12" s="10" t="n">
-        <v>1</v>
+      <c r="M12" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
-      <c r="R12" s="10" t="n">
-        <v>1</v>
+      <c r="R12" t="n">
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -4826,17 +4856,17 @@
       <c r="U12" t="n">
         <v>0</v>
       </c>
-      <c r="V12" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="W12" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="X12" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y12" s="10" t="n">
-        <v>1</v>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
         <v>0</v>
@@ -4847,20 +4877,20 @@
       <c r="AB12" t="n">
         <v>0</v>
       </c>
-      <c r="AC12" s="13" t="n">
-        <v>1</v>
+      <c r="AC12" t="n">
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
       </c>
-      <c r="AE12" t="n">
+      <c r="AE12" s="20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Medical Governance Office</t>
+          <t>Medical Excellence Office</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -4869,7 +4899,7 @@
       <c r="C13" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="12" t="n">
+      <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
@@ -4878,47 +4908,47 @@
       <c r="F13" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="10" t="n">
-        <v>1</v>
+      <c r="G13" s="21" t="n">
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" s="10" t="n">
+      <c r="I13" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" s="19" t="n">
         <v>1</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
+      <c r="N13" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
+      <c r="Q13" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
-      <c r="T13" t="n">
-        <v>0</v>
+      <c r="T13" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -4926,38 +4956,38 @@
       <c r="V13" t="n">
         <v>0</v>
       </c>
-      <c r="W13" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="X13" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y13" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0</v>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y13" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z13" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA13" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
       </c>
-      <c r="AC13" s="11" t="n">
+      <c r="AC13" t="n">
         <v>0</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
       </c>
-      <c r="AE13" t="n">
-        <v>0</v>
+      <c r="AE13" s="22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Medical Governance Unit</t>
+          <t>Medical Excellence Team</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -4966,7 +4996,7 @@
       <c r="C14" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="12" t="n">
+      <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
@@ -4975,47 +5005,47 @@
       <c r="F14" t="n">
         <v>0</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
+      <c r="I14" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
-      <c r="O14" t="n">
-        <v>0</v>
+      <c r="O14" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
+      <c r="Q14" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
-      <c r="T14" t="n">
-        <v>0</v>
+      <c r="T14" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -5026,35 +5056,35 @@
       <c r="W14" t="n">
         <v>0</v>
       </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0</v>
+      <c r="X14" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y14" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z14" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA14" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
       </c>
-      <c r="AC14" s="11" t="n">
+      <c r="AC14" t="n">
         <v>0</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
       </c>
-      <c r="AE14" t="n">
-        <v>0</v>
+      <c r="AE14" s="22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Medical Innovation Group</t>
+          <t>Medical Governance Office</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -5063,7 +5093,7 @@
       <c r="C15" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="12" t="n">
+      <c r="D15" t="n">
         <v>0</v>
       </c>
       <c r="E15" t="n">
@@ -5072,29 +5102,29 @@
       <c r="F15" t="n">
         <v>0</v>
       </c>
-      <c r="G15" s="10" t="n">
-        <v>1</v>
+      <c r="G15" s="21" t="n">
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
-      <c r="I15" t="n">
-        <v>0</v>
+      <c r="I15" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
-      <c r="K15" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -5102,14 +5132,14 @@
       <c r="P15" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" s="10" t="n">
-        <v>1</v>
+      <c r="Q15" t="n">
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
-      <c r="S15" t="n">
-        <v>0</v>
+      <c r="S15" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
@@ -5126,32 +5156,32 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
-      <c r="Y15" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0</v>
+      <c r="Y15" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z15" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA15" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
       </c>
-      <c r="AC15" s="11" t="n">
+      <c r="AC15" t="n">
         <v>0</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
       </c>
-      <c r="AE15" t="n">
+      <c r="AE15" s="20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Medical Research Evaluation</t>
+          <t>Medical Governance Unit</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -5160,32 +5190,32 @@
       <c r="C16" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" s="10" t="n">
-        <v>1</v>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
-      <c r="K16" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" s="10" t="n">
-        <v>1</v>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -5214,14 +5244,14 @@
       <c r="U16" t="n">
         <v>0</v>
       </c>
-      <c r="V16" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="W16" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="X16" s="10" t="n">
-        <v>1</v>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
@@ -5235,20 +5265,20 @@
       <c r="AB16" t="n">
         <v>0</v>
       </c>
-      <c r="AC16" s="11" t="n">
+      <c r="AC16" t="n">
         <v>0</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
       </c>
-      <c r="AE16" t="n">
+      <c r="AE16" s="20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Medical Scientific Information Center</t>
+          <t>Medical Innovation Group</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -5257,7 +5287,7 @@
       <c r="C17" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="12" t="n">
+      <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
@@ -5266,14 +5296,14 @@
       <c r="F17" t="n">
         <v>0</v>
       </c>
-      <c r="G17" s="10" t="n">
-        <v>1</v>
+      <c r="G17" s="21" t="n">
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
-      <c r="I17" t="n">
-        <v>0</v>
+      <c r="I17" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -5284,14 +5314,14 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
-      <c r="M17" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" s="10" t="n">
-        <v>1</v>
+      <c r="M17" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -5302,59 +5332,59 @@
       <c r="R17" t="n">
         <v>0</v>
       </c>
-      <c r="S17" t="n">
-        <v>0</v>
+      <c r="S17" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
       </c>
-      <c r="U17" s="10" t="n">
-        <v>1</v>
+      <c r="U17" t="n">
+        <v>0</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
-      <c r="W17" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="X17" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y17" s="10" t="n">
-        <v>1</v>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
       </c>
-      <c r="AA17" t="n">
-        <v>0</v>
+      <c r="AA17" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
       </c>
-      <c r="AC17" s="11" t="n">
+      <c r="AC17" t="n">
         <v>0</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
       </c>
-      <c r="AE17" t="n">
+      <c r="AE17" s="20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>New Product Value Planning</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
+          <t>Medical Research Evaluation</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
-      <c r="D18" s="12" t="n">
+      <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
@@ -5363,29 +5393,29 @@
       <c r="F18" t="n">
         <v>0</v>
       </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
+      <c r="G18" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
+      <c r="J18" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -5414,14 +5444,14 @@
       <c r="W18" t="n">
         <v>0</v>
       </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
+      <c r="X18" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y18" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z18" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -5429,20 +5459,20 @@
       <c r="AB18" t="n">
         <v>0</v>
       </c>
-      <c r="AC18" s="11" t="n">
+      <c r="AC18" t="n">
         <v>0</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
       </c>
-      <c r="AE18" t="n">
+      <c r="AE18" s="20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Operational Excellence</t>
+          <t>Medical Scientific Information Center</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -5451,7 +5481,7 @@
       <c r="C19" t="n">
         <v>0</v>
       </c>
-      <c r="D19" s="12" t="n">
+      <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
@@ -5460,14 +5490,14 @@
       <c r="F19" t="n">
         <v>0</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G19" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
-      <c r="I19" t="n">
-        <v>0</v>
+      <c r="I19" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -5484,14 +5514,14 @@
       <c r="N19" t="n">
         <v>0</v>
       </c>
-      <c r="O19" t="n">
-        <v>0</v>
+      <c r="O19" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
+      <c r="Q19" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -5508,38 +5538,38 @@
       <c r="V19" t="n">
         <v>0</v>
       </c>
-      <c r="W19" t="n">
-        <v>0</v>
+      <c r="W19" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
       </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0</v>
+      <c r="Y19" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z19" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA19" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
       </c>
-      <c r="AC19" s="11" t="n">
+      <c r="AC19" t="n">
         <v>0</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
       </c>
-      <c r="AE19" t="n">
+      <c r="AE19" s="20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Post-Marketing Study Strategy Management</t>
+          <t>New Product Value Planning</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -5548,7 +5578,7 @@
       <c r="C20" t="n">
         <v>0</v>
       </c>
-      <c r="D20" s="12" t="n">
+      <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
@@ -5557,7 +5587,7 @@
       <c r="F20" t="n">
         <v>0</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G20" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
@@ -5575,11 +5605,11 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
+      <c r="M20" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -5614,8 +5644,8 @@
       <c r="Y20" t="n">
         <v>0</v>
       </c>
-      <c r="Z20" s="10" t="n">
-        <v>1</v>
+      <c r="Z20" t="n">
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -5623,20 +5653,20 @@
       <c r="AB20" t="n">
         <v>0</v>
       </c>
-      <c r="AC20" s="11" t="n">
+      <c r="AC20" t="n">
         <v>0</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
       </c>
-      <c r="AE20" t="n">
+      <c r="AE20" s="20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Product Management Review</t>
+          <t>Operational Excellence</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -5645,7 +5675,7 @@
       <c r="C21" t="n">
         <v>0</v>
       </c>
-      <c r="D21" s="12" t="n">
+      <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
@@ -5654,8 +5684,8 @@
       <c r="F21" t="n">
         <v>0</v>
       </c>
-      <c r="G21" s="10" t="n">
-        <v>1</v>
+      <c r="G21" s="21" t="n">
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -5684,8 +5714,8 @@
       <c r="P21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" s="10" t="n">
-        <v>1</v>
+      <c r="Q21" t="n">
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -5708,8 +5738,8 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
-      <c r="Y21" s="10" t="n">
-        <v>1</v>
+      <c r="Y21" t="n">
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
         <v>0</v>
@@ -5720,20 +5750,20 @@
       <c r="AB21" t="n">
         <v>0</v>
       </c>
-      <c r="AC21" s="11" t="n">
+      <c r="AC21" t="n">
         <v>0</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
       </c>
-      <c r="AE21" t="n">
+      <c r="AE21" s="20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Regulatory Affairs Unit 1</t>
+          <t>Post-Marketing Study Strategy Management</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -5742,7 +5772,7 @@
       <c r="C22" t="n">
         <v>0</v>
       </c>
-      <c r="D22" s="12" t="n">
+      <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
@@ -5751,23 +5781,23 @@
       <c r="F22" t="n">
         <v>0</v>
       </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" s="10" t="n">
-        <v>1</v>
+      <c r="G22" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
-      <c r="K22" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" s="10" t="n">
-        <v>1</v>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -5778,8 +5808,8 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="P22" s="10" t="n">
-        <v>1</v>
+      <c r="P22" t="n">
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -5799,11 +5829,11 @@
       <c r="V22" t="n">
         <v>0</v>
       </c>
-      <c r="W22" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="X22" s="10" t="n">
-        <v>1</v>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
         <v>0</v>
@@ -5814,23 +5844,23 @@
       <c r="AA22" t="n">
         <v>0</v>
       </c>
-      <c r="AB22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC22" s="11" t="n">
+      <c r="AB22" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC22" t="n">
         <v>0</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
       </c>
-      <c r="AE22" t="n">
+      <c r="AE22" s="20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Regulatory Affairs Unit 2</t>
+          <t>Product Management Review</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -5839,7 +5869,7 @@
       <c r="C23" t="n">
         <v>0</v>
       </c>
-      <c r="D23" s="12" t="n">
+      <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
@@ -5848,26 +5878,26 @@
       <c r="F23" t="n">
         <v>0</v>
       </c>
-      <c r="G23" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I23" s="10" t="n">
+      <c r="G23" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="19" t="n">
         <v>1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
-      <c r="K23" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L23" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M23" s="10" t="n">
-        <v>1</v>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -5875,17 +5905,17 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
-      <c r="P23" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q23" s="10" t="n">
-        <v>1</v>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
-      <c r="S23" t="n">
-        <v>0</v>
+      <c r="S23" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
@@ -5893,41 +5923,41 @@
       <c r="U23" t="n">
         <v>0</v>
       </c>
-      <c r="V23" s="10" t="n">
-        <v>1</v>
+      <c r="V23" t="n">
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
-      <c r="X23" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y23" s="10" t="n">
-        <v>1</v>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
       </c>
-      <c r="AA23" t="n">
-        <v>0</v>
+      <c r="AA23" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
       </c>
-      <c r="AC23" s="11" t="n">
+      <c r="AC23" t="n">
         <v>0</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
       </c>
-      <c r="AE23" t="n">
+      <c r="AE23" s="20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Regulatory Affairs Unit 3</t>
+          <t>Regulatory Affairs Unit 1</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -5936,7 +5966,7 @@
       <c r="C24" t="n">
         <v>0</v>
       </c>
-      <c r="D24" s="12" t="n">
+      <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
@@ -5945,41 +5975,41 @@
       <c r="F24" t="n">
         <v>0</v>
       </c>
-      <c r="G24" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I24" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M24" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
+      <c r="G24" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N24" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
-      <c r="P24" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q24" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5990,20 +6020,20 @@
       <c r="U24" t="n">
         <v>0</v>
       </c>
-      <c r="V24" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="W24" s="10" t="n">
-        <v>1</v>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
       </c>
-      <c r="Y24" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>0</v>
+      <c r="Y24" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z24" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -6011,20 +6041,20 @@
       <c r="AB24" t="n">
         <v>0</v>
       </c>
-      <c r="AC24" s="11" t="n">
+      <c r="AC24" t="n">
         <v>0</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
       </c>
-      <c r="AE24" t="n">
+      <c r="AE24" s="20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Scientific Information Center</t>
+          <t>Regulatory Affairs Unit 2</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -6033,7 +6063,7 @@
       <c r="C25" t="n">
         <v>0</v>
       </c>
-      <c r="D25" s="12" t="n">
+      <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
@@ -6042,86 +6072,86 @@
       <c r="F25" t="n">
         <v>0</v>
       </c>
-      <c r="G25" s="10" t="n">
-        <v>1</v>
+      <c r="G25" s="21" t="n">
+        <v>0</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L25" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M25" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" s="10" t="n">
+      <c r="I25" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N25" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" s="19" t="n">
         <v>1</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S25" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
       </c>
-      <c r="U25" s="10" t="n">
-        <v>1</v>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
       </c>
-      <c r="W25" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="X25" s="10" t="n">
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" s="19" t="n">
         <v>1</v>
       </c>
       <c r="Y25" t="n">
         <v>0</v>
       </c>
-      <c r="Z25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>0</v>
+      <c r="Z25" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA25" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
       </c>
-      <c r="AC25" s="11" t="n">
+      <c r="AC25" t="n">
         <v>0</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
       </c>
-      <c r="AE25" t="n">
+      <c r="AE25" s="20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Strategic Management Office 1</t>
+          <t>Regulatory Affairs Unit 3</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -6130,7 +6160,7 @@
       <c r="C26" t="n">
         <v>0</v>
       </c>
-      <c r="D26" s="12" t="n">
+      <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
@@ -6139,32 +6169,32 @@
       <c r="F26" t="n">
         <v>0</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G26" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="I26" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
+      <c r="M26" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N26" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O26" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -6172,14 +6202,14 @@
       <c r="Q26" t="n">
         <v>0</v>
       </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" s="10" t="n">
-        <v>1</v>
+      <c r="R26" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S26" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -6190,35 +6220,35 @@
       <c r="W26" t="n">
         <v>0</v>
       </c>
-      <c r="X26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>0</v>
+      <c r="X26" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y26" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="Z26" t="n">
         <v>0</v>
       </c>
-      <c r="AA26" t="n">
-        <v>0</v>
+      <c r="AA26" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
       </c>
-      <c r="AC26" s="11" t="n">
+      <c r="AC26" t="n">
         <v>0</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>
       </c>
-      <c r="AE26" t="n">
+      <c r="AE26" s="20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Strategic Management Office 2</t>
+          <t>Scientific Information Center</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -6227,7 +6257,7 @@
       <c r="C27" t="n">
         <v>0</v>
       </c>
-      <c r="D27" s="12" t="n">
+      <c r="D27" t="n">
         <v>0</v>
       </c>
       <c r="E27" t="n">
@@ -6236,14 +6266,14 @@
       <c r="F27" t="n">
         <v>0</v>
       </c>
-      <c r="G27" t="n">
+      <c r="G27" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
-      <c r="I27" t="n">
-        <v>0</v>
+      <c r="I27" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -6254,26 +6284,26 @@
       <c r="L27" t="n">
         <v>0</v>
       </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
+      <c r="M27" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N27" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
+      <c r="Q27" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
-      <c r="S27" t="n">
-        <v>0</v>
+      <c r="S27" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="T27" t="n">
         <v>0</v>
@@ -6284,17 +6314,17 @@
       <c r="V27" t="n">
         <v>0</v>
       </c>
-      <c r="W27" t="n">
-        <v>0</v>
+      <c r="W27" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="X27" t="n">
         <v>0</v>
       </c>
-      <c r="Y27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0</v>
+      <c r="Y27" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z27" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -6302,20 +6332,20 @@
       <c r="AB27" t="n">
         <v>0</v>
       </c>
-      <c r="AC27" s="11" t="n">
+      <c r="AC27" t="n">
         <v>0</v>
       </c>
       <c r="AD27" t="n">
         <v>0</v>
       </c>
-      <c r="AE27" t="n">
+      <c r="AE27" s="20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Strategic Management Office 3</t>
+          <t>Strategic Management Office 1</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -6324,7 +6354,7 @@
       <c r="C28" t="n">
         <v>0</v>
       </c>
-      <c r="D28" s="12" t="n">
+      <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
@@ -6333,7 +6363,7 @@
       <c r="F28" t="n">
         <v>0</v>
       </c>
-      <c r="G28" t="n">
+      <c r="G28" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
@@ -6378,8 +6408,8 @@
       <c r="U28" t="n">
         <v>0</v>
       </c>
-      <c r="V28" t="n">
-        <v>0</v>
+      <c r="V28" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="W28" t="n">
         <v>0</v>
@@ -6399,20 +6429,20 @@
       <c r="AB28" t="n">
         <v>0</v>
       </c>
-      <c r="AC28" s="11" t="n">
+      <c r="AC28" t="n">
         <v>0</v>
       </c>
       <c r="AD28" t="n">
         <v>0</v>
       </c>
-      <c r="AE28" t="n">
+      <c r="AE28" s="20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Strategic Medical Excellence</t>
+          <t>Strategic Management Office 2</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -6421,95 +6451,95 @@
       <c r="C29" t="n">
         <v>0</v>
       </c>
-      <c r="D29" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L29" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M29" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA29" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB29" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC29" s="17" t="n">
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
         <v>0</v>
       </c>
       <c r="AD29" t="n">
         <v>0</v>
       </c>
-      <c r="AE29" t="n">
+      <c r="AE29" s="20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Operational Effectiveness</t>
+          <t>Strategic Management Office 3</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -6527,7 +6557,7 @@
       <c r="F30" t="n">
         <v>0</v>
       </c>
-      <c r="G30" t="n">
+      <c r="G30" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
@@ -6596,17 +6626,17 @@
       <c r="AC30" t="n">
         <v>0</v>
       </c>
-      <c r="AD30" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE30" s="19" t="n">
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Strategic Management Team 2</t>
+          <t>Strategic Medical Excellence</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -6624,79 +6654,79 @@
       <c r="F31" t="n">
         <v>0</v>
       </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD31" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE31" s="21" t="n">
+      <c r="G31" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="N31" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="O31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6732,12 +6762,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Strategic Management Team 1</t>
+          <t>Clinical Strategy Group</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Cluster 3</t>
+          <t>Cluster 0</t>
         </is>
       </c>
     </row>
@@ -6747,12 +6777,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Strategic Management Team 3</t>
+          <t>Strategic Management Team 1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Cluster 3</t>
+          <t>Cluster 0</t>
         </is>
       </c>
     </row>
@@ -6762,12 +6792,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Clinical Research Division</t>
+          <t>Strategic Management Team 3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cluster 7</t>
+          <t>Cluster 0</t>
         </is>
       </c>
     </row>
@@ -6777,12 +6807,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Clinical Strategy Division</t>
+          <t>Operational Effectiveness</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cluster 7</t>
+          <t>Cluster 5</t>
         </is>
       </c>
     </row>
@@ -6792,12 +6822,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Clinical Strategy Group</t>
+          <t>Strategic Management Team 2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cluster 7</t>
+          <t>Cluster 5</t>
         </is>
       </c>
     </row>
@@ -6807,12 +6837,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Medical Communications Office</t>
+          <t>Clinical Research Division</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cluster 7</t>
+          <t>Cluster 6</t>
         </is>
       </c>
     </row>
@@ -6822,12 +6852,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Medical Evaluation Unit 1</t>
+          <t>Clinical Strategy Division</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cluster 7</t>
+          <t>Cluster 6</t>
         </is>
       </c>
     </row>
@@ -6837,12 +6867,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Medical Evaluation Unit 2</t>
+          <t>Medical Communications Office</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cluster 7</t>
+          <t>Cluster 6</t>
         </is>
       </c>
     </row>
@@ -6852,12 +6882,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Medical Evaluation Unit 3</t>
+          <t>Medical Evaluation Unit 1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cluster 7</t>
+          <t>Cluster 6</t>
         </is>
       </c>
     </row>
@@ -6867,12 +6897,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Medical Excellence Office</t>
+          <t>Medical Evaluation Unit 2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cluster 7</t>
+          <t>Cluster 6</t>
         </is>
       </c>
     </row>
@@ -6882,12 +6912,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Medical Excellence Team</t>
+          <t>Medical Evaluation Unit 3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cluster 7</t>
+          <t>Cluster 6</t>
         </is>
       </c>
     </row>
@@ -6897,12 +6927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Medical Governance Office</t>
+          <t>Medical Excellence Office</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cluster 7</t>
+          <t>Cluster 6</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6942,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Medical Governance Unit</t>
+          <t>Medical Excellence Team</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cluster 7</t>
+          <t>Cluster 6</t>
         </is>
       </c>
     </row>
@@ -6927,12 +6957,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Medical Innovation Group</t>
+          <t>Medical Governance Office</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cluster 7</t>
+          <t>Cluster 6</t>
         </is>
       </c>
     </row>
@@ -6942,12 +6972,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Medical Research Evaluation</t>
+          <t>Medical Governance Unit</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cluster 7</t>
+          <t>Cluster 6</t>
         </is>
       </c>
     </row>
@@ -6957,12 +6987,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Medical Scientific Information Center</t>
+          <t>Medical Innovation Group</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cluster 7</t>
+          <t>Cluster 6</t>
         </is>
       </c>
     </row>
@@ -6972,12 +7002,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>New Product Value Planning</t>
+          <t>Medical Research Evaluation</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cluster 7</t>
+          <t>Cluster 6</t>
         </is>
       </c>
     </row>
@@ -6987,12 +7017,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Operational Excellence</t>
+          <t>Medical Scientific Information Center</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cluster 7</t>
+          <t>Cluster 6</t>
         </is>
       </c>
     </row>
@@ -7002,12 +7032,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Post-Marketing Study Strategy Management</t>
+          <t>New Product Value Planning</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cluster 7</t>
+          <t>Cluster 6</t>
         </is>
       </c>
     </row>
@@ -7017,12 +7047,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Product Management Review</t>
+          <t>Operational Excellence</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cluster 7</t>
+          <t>Cluster 6</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7062,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Regulatory Affairs Unit 1</t>
+          <t>Post-Marketing Study Strategy Management</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cluster 7</t>
+          <t>Cluster 6</t>
         </is>
       </c>
     </row>
@@ -7047,12 +7077,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Regulatory Affairs Unit 2</t>
+          <t>Product Management Review</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cluster 7</t>
+          <t>Cluster 6</t>
         </is>
       </c>
     </row>
@@ -7062,12 +7092,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Regulatory Affairs Unit 3</t>
+          <t>Regulatory Affairs Unit 1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cluster 7</t>
+          <t>Cluster 6</t>
         </is>
       </c>
     </row>
@@ -7077,12 +7107,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Scientific Information Center</t>
+          <t>Regulatory Affairs Unit 2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cluster 7</t>
+          <t>Cluster 6</t>
         </is>
       </c>
     </row>
@@ -7092,12 +7122,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Strategic Management Office 1</t>
+          <t>Regulatory Affairs Unit 3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cluster 7</t>
+          <t>Cluster 6</t>
         </is>
       </c>
     </row>
@@ -7107,12 +7137,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Strategic Management Office 2</t>
+          <t>Scientific Information Center</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cluster 7</t>
+          <t>Cluster 6</t>
         </is>
       </c>
     </row>
@@ -7122,12 +7152,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Strategic Management Office 3</t>
+          <t>Strategic Management Office 1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cluster 7</t>
+          <t>Cluster 6</t>
         </is>
       </c>
     </row>
@@ -7137,12 +7167,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Strategic Medical Excellence</t>
+          <t>Strategic Management Office 2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cluster 7</t>
+          <t>Cluster 6</t>
         </is>
       </c>
     </row>
@@ -7152,12 +7182,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Operational Effectiveness</t>
+          <t>Strategic Management Office 3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cluster 9</t>
+          <t>Cluster 6</t>
         </is>
       </c>
     </row>
@@ -7167,12 +7197,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Strategic Management Team 2</t>
+          <t>Strategic Medical Excellence</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cluster 9</t>
+          <t>Cluster 6</t>
         </is>
       </c>
     </row>
